--- a/artfynd/A 25037-2024 artfynd.xlsx
+++ b/artfynd/A 25037-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124077410</v>
+        <v>124077418</v>
       </c>
       <c r="B2" t="n">
-        <v>57602</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599039</v>
+        <v>599086</v>
       </c>
       <c r="R2" t="n">
-        <v>7178889</v>
+        <v>7178997</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124077418</v>
+        <v>124077410</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>57602</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,20 +808,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599086</v>
+        <v>599039</v>
       </c>
       <c r="R3" t="n">
-        <v>7178997</v>
+        <v>7178889</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 25037-2024 artfynd.xlsx
+++ b/artfynd/A 25037-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124077418</v>
+        <v>124077410</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>57602</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599086</v>
+        <v>599039</v>
       </c>
       <c r="R2" t="n">
-        <v>7178997</v>
+        <v>7178889</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124077410</v>
+        <v>124077418</v>
       </c>
       <c r="B3" t="n">
-        <v>57602</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,20 +808,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599039</v>
+        <v>599086</v>
       </c>
       <c r="R3" t="n">
-        <v>7178889</v>
+        <v>7178997</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 25037-2024 artfynd.xlsx
+++ b/artfynd/A 25037-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124077410</v>
+        <v>124077418</v>
       </c>
       <c r="B2" t="n">
-        <v>57624</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599039</v>
+        <v>599086</v>
       </c>
       <c r="R2" t="n">
-        <v>7178889</v>
+        <v>7178997</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124077418</v>
+        <v>124077410</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57624</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,20 +808,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599086</v>
+        <v>599039</v>
       </c>
       <c r="R3" t="n">
-        <v>7178997</v>
+        <v>7178889</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 25037-2024 artfynd.xlsx
+++ b/artfynd/A 25037-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124077418</v>
+        <v>124077410</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599086</v>
+        <v>599039</v>
       </c>
       <c r="R2" t="n">
-        <v>7178997</v>
+        <v>7178889</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124077410</v>
+        <v>124077418</v>
       </c>
       <c r="B3" t="n">
-        <v>57624</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,20 +808,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599039</v>
+        <v>599086</v>
       </c>
       <c r="R3" t="n">
-        <v>7178889</v>
+        <v>7178997</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 25037-2024 artfynd.xlsx
+++ b/artfynd/A 25037-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124077418</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25037-2024 artfynd.xlsx
+++ b/artfynd/A 25037-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124077418</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25037-2024 artfynd.xlsx
+++ b/artfynd/A 25037-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124077418</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25037-2024 artfynd.xlsx
+++ b/artfynd/A 25037-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124077418</v>
       </c>
       <c r="B2" t="n">
-        <v>57897</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,16 +794,11 @@
         <v>124077410</v>
       </c>
       <c r="B3" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
